--- a/input/align_educLevel.xlsx
+++ b/input/align_educLevel.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F2D5C3-0E13-4567-B019-D79EDF01BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338B6946-D1E3-417B-B724-64D5E3C89689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{8B3B1A3D-54CF-4240-A44B-2FEE87419FDF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{8B3B1A3D-54CF-4240-A44B-2FEE87419FDF}"/>
   </bookViews>
   <sheets>
     <sheet name="UK_High" sheetId="1" r:id="rId1"/>
     <sheet name="UK_Low" sheetId="2" r:id="rId2"/>
-    <sheet name="IT_High" sheetId="3" r:id="rId3"/>
-    <sheet name="IT_Low" sheetId="4" r:id="rId4"/>
+    <sheet name="EL_High" sheetId="3" r:id="rId3"/>
+    <sheet name="EL_Low" sheetId="4" r:id="rId4"/>
     <sheet name="PL_High" sheetId="5" r:id="rId5"/>
     <sheet name="PL_Low" sheetId="6" r:id="rId6"/>
   </sheets>

--- a/input/align_educLevel.xlsx
+++ b/input/align_educLevel.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\labsim\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0566A792-5244-480B-8064-D9BA1362E703}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34084032-26B2-B143-B7F0-AD0705527004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7455" yWindow="5925" windowWidth="27750" windowHeight="11130" activeTab="3" xr2:uid="{8B3B1A3D-54CF-4240-A44B-2FEE87419FDF}"/>
+    <workbookView xWindow="2480" yWindow="5920" windowWidth="27760" windowHeight="11140" activeTab="1" xr2:uid="{8B3B1A3D-54CF-4240-A44B-2FEE87419FDF}"/>
   </bookViews>
   <sheets>
-    <sheet name="UK_High" sheetId="1" r:id="rId1"/>
-    <sheet name="UK_Low" sheetId="2" r:id="rId2"/>
-    <sheet name="IT_High" sheetId="3" r:id="rId3"/>
-    <sheet name="IT_Low" sheetId="4" r:id="rId4"/>
+    <sheet name="High" sheetId="1" r:id="rId1"/>
+    <sheet name="Low" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
   <si>
     <t>Year / Gender</t>
   </si>
@@ -101,9 +99,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -141,7 +139,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -247,7 +245,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -389,7 +387,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -398,9 +396,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E6204B-313B-4423-82F5-B005D81FF0B5}">
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,7 +409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2015</v>
       </c>
@@ -422,7 +420,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2016</v>
       </c>
@@ -433,7 +431,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -444,7 +442,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2018</v>
       </c>
@@ -455,7 +453,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2019</v>
       </c>
@@ -466,7 +464,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -477,7 +475,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -488,7 +486,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -499,7 +497,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2023</v>
       </c>
@@ -510,7 +508,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -521,7 +519,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2025</v>
       </c>
@@ -532,7 +530,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2026</v>
       </c>
@@ -543,7 +541,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2027</v>
       </c>
@@ -554,7 +552,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2028</v>
       </c>
@@ -565,7 +563,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2029</v>
       </c>
@@ -576,7 +574,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2030</v>
       </c>
@@ -587,7 +585,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2031</v>
       </c>
@@ -598,7 +596,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2032</v>
       </c>
@@ -609,7 +607,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2033</v>
       </c>
@@ -620,7 +618,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2034</v>
       </c>
@@ -631,7 +629,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2035</v>
       </c>
@@ -642,7 +640,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2036</v>
       </c>
@@ -653,7 +651,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2037</v>
       </c>
@@ -664,7 +662,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2038</v>
       </c>
@@ -675,7 +673,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2039</v>
       </c>
@@ -686,7 +684,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2040</v>
       </c>
@@ -697,7 +695,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2041</v>
       </c>
@@ -708,7 +706,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2042</v>
       </c>
@@ -719,7 +717,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2043</v>
       </c>
@@ -730,7 +728,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2044</v>
       </c>
@@ -741,7 +739,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2045</v>
       </c>
@@ -752,7 +750,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2046</v>
       </c>
@@ -763,7 +761,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2047</v>
       </c>
@@ -774,7 +772,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2048</v>
       </c>
@@ -785,7 +783,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2049</v>
       </c>
@@ -796,7 +794,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2050</v>
       </c>
@@ -815,9 +813,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78141D46-7C1C-48EE-BBCF-2138B1181D69}">
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -828,7 +826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2015</v>
       </c>
@@ -839,7 +837,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2016</v>
       </c>
@@ -850,7 +848,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -861,7 +859,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2018</v>
       </c>
@@ -872,7 +870,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2019</v>
       </c>
@@ -883,7 +881,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -894,7 +892,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -905,7 +903,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -916,7 +914,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2023</v>
       </c>
@@ -927,7 +925,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -938,7 +936,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2025</v>
       </c>
@@ -949,7 +947,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2026</v>
       </c>
@@ -960,7 +958,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2027</v>
       </c>
@@ -971,7 +969,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2028</v>
       </c>
@@ -982,7 +980,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2029</v>
       </c>
@@ -993,7 +991,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2030</v>
       </c>
@@ -1004,7 +1002,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2031</v>
       </c>
@@ -1015,7 +1013,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2032</v>
       </c>
@@ -1026,7 +1024,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2033</v>
       </c>
@@ -1037,7 +1035,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2034</v>
       </c>
@@ -1048,7 +1046,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2035</v>
       </c>
@@ -1059,7 +1057,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2036</v>
       </c>
@@ -1070,7 +1068,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2037</v>
       </c>
@@ -1081,7 +1079,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2038</v>
       </c>
@@ -1092,7 +1090,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2039</v>
       </c>
@@ -1103,7 +1101,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2040</v>
       </c>
@@ -1114,7 +1112,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2041</v>
       </c>
@@ -1125,7 +1123,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2042</v>
       </c>
@@ -1136,7 +1134,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2043</v>
       </c>
@@ -1147,7 +1145,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2044</v>
       </c>
@@ -1158,7 +1156,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2045</v>
       </c>
@@ -1169,7 +1167,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2046</v>
       </c>
@@ -1180,7 +1178,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2047</v>
       </c>
@@ -1191,7 +1189,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2048</v>
       </c>
@@ -1202,7 +1200,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2049</v>
       </c>
@@ -1213,841 +1211,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>2050</v>
-      </c>
-      <c r="B37">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C37">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6917FA4B-F602-4CCD-B89C-C793122A6893}">
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2015</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2016</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2017</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2018</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2019</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2022</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2023</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2024</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2025</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2026</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2027</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2028</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2029</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2030</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2031</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2032</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2033</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2034</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2035</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2036</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2037</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2038</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2039</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2040</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2041</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2042</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2043</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2044</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2045</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2046</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>2047</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>2048</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>2049</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>2050</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B140867-5511-4C6F-900E-68586488B939}">
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2015</v>
-      </c>
-      <c r="B2">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C2">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2016</v>
-      </c>
-      <c r="B3">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C3">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2017</v>
-      </c>
-      <c r="B4">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C4">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2018</v>
-      </c>
-      <c r="B5">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C5">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2019</v>
-      </c>
-      <c r="B6">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C6">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2020</v>
-      </c>
-      <c r="B7">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C7">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2021</v>
-      </c>
-      <c r="B8">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C8">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2022</v>
-      </c>
-      <c r="B9">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C9">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2023</v>
-      </c>
-      <c r="B10">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C10">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2024</v>
-      </c>
-      <c r="B11">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C11">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2025</v>
-      </c>
-      <c r="B12">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C12">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2026</v>
-      </c>
-      <c r="B13">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C13">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2027</v>
-      </c>
-      <c r="B14">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C14">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2028</v>
-      </c>
-      <c r="B15">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C15">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2029</v>
-      </c>
-      <c r="B16">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C16">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2030</v>
-      </c>
-      <c r="B17">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C17">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2031</v>
-      </c>
-      <c r="B18">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C18">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2032</v>
-      </c>
-      <c r="B19">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C19">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2033</v>
-      </c>
-      <c r="B20">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C20">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2034</v>
-      </c>
-      <c r="B21">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C21">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2035</v>
-      </c>
-      <c r="B22">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C22">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2036</v>
-      </c>
-      <c r="B23">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C23">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2037</v>
-      </c>
-      <c r="B24">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C24">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2038</v>
-      </c>
-      <c r="B25">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C25">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2039</v>
-      </c>
-      <c r="B26">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C26">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2040</v>
-      </c>
-      <c r="B27">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C27">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2041</v>
-      </c>
-      <c r="B28">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C28">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2042</v>
-      </c>
-      <c r="B29">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C29">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2043</v>
-      </c>
-      <c r="B30">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C30">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2044</v>
-      </c>
-      <c r="B31">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C31">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2045</v>
-      </c>
-      <c r="B32">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C32">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2046</v>
-      </c>
-      <c r="B33">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C33">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>2047</v>
-      </c>
-      <c r="B34">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C34">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>2048</v>
-      </c>
-      <c r="B35">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C35">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>2049</v>
-      </c>
-      <c r="B36">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="C36">
-        <v>3.6799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2050</v>
       </c>
